--- a/sesans_comparison.xlsx
+++ b/sesans_comparison.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="51">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -61,232 +61,172 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="006EC17B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0089C87D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4D57F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FA9072"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0063BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0071C27B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007BC57C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F97C6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0069BF7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082C77C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0089C97D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A3D07E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAE983"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD27F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0073C27B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092CB7D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FA9B74"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006FC17B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007CC57C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066BF7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0080C67C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009FCF7E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE582"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0068BF7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0065BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCB87A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCBA7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCC57C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0072C27B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEDE81"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F86E6C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FA9773"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0074C37C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="006BC07B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008BC97D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A5D17E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ADD37F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0065BE7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0063BE7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0064BE7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAA075"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007EC57C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009DCE7E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0097CD7E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B8D67F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBB078"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0067BF7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8E983"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006AC07B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070C17B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0089C97D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0066BF7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBB279"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075C37C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0086C87D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0068BF7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007FC67C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007BC57C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008CC97D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0069BF7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006EC17B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0087C87D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008DCA7D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B9D780"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCEA83"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006FC17B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0082C77C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F98470"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0078C47C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0079C47C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBA676"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C0D980"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0E683"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007AC47C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0076C37C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F87B6E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E1E282"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FA9172"/>
       </patternFill>
     </fill>
   </fills>
@@ -316,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -399,36 +339,33 @@
     <xf numFmtId="164" fontId="0" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="11" fontId="0" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="11" fontId="0" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -441,55 +378,10 @@
     <xf numFmtId="11" fontId="0" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="49" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="50" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -857,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -867,10 +759,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,27 +801,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>libhankel qwe</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht key 101</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht key 51</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht guptasarma</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht guptasarma fast</t>
+          <t>libhankel fftlog</t>
         </is>
       </c>
     </row>
@@ -944,34 +812,22 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>16.80179840004712</v>
+        <v>5.62656740003149</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.8761942001001444</v>
+        <v>0.6922193999344017</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2.542928599905281</v>
+        <v>1.130087400088087</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3.916326599937747</v>
+        <v>1.837648599757813</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4.331047599953308</v>
+        <v>4.853807000472443</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>217.2422297999219</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>0.5845692001457792</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0.4687049999120063</v>
-      </c>
-      <c r="J3" s="12" t="n">
-        <v>0.5000006000045687</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>0.4435425998963183</v>
+        <v>0.5042741999204736</v>
       </c>
     </row>
     <row r="4">
@@ -980,35 +836,23 @@
           <t>spheres2micron.ses</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>8.18726779998542</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>0.4541614000117988</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>1.252417400064587</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>2.243767999971169</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>10.300152399941</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>73.66987140012498</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>0.4505511999013834</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0.3824658000667114</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>0.3923312000551959</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>0.3995054001279641</v>
+      <c r="B4" s="4" t="n">
+        <v>10.07558420023997</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>0.2878024002711754</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>0.7333581997954752</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>1.052332400286105</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>9.359375799976988</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0.4895198006124701</v>
       </c>
     </row>
     <row r="5">
@@ -1018,34 +862,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.077174599930004</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>1.61001619999297</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>1.903660600146395</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>2.67911520004418</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>6.023435200040694</v>
+        <v>11.08511900019948</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1.762975599558558</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>2.000625599612249</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>2.873339600046165</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>5.758084799890639</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>121.7988958000205</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.7655776000319747</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>0.6759265999789932</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.707108400092693</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>0.6477684000856243</v>
+        <v>0.7212870004877914</v>
       </c>
     </row>
     <row r="6">
@@ -1054,35 +886,23 @@
           <t>se008724_01.ses</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
-        <v>8.155548800095858</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>0.829758799955016</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>1.160565600002883</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>2.444679399923189</v>
+      <c r="B6" s="18" t="n">
+        <v>10.18937740009278</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.7667985999432858</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>1.315224000427406</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>2.90795260007144</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16.53249400005734</v>
+        <v>16.89279679994797</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>184.8109964001196</v>
-      </c>
-      <c r="H6" s="24" t="n">
-        <v>0.648021599954518</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>0.501276599970879</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>0.5184747999010142</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>0.4674212001191336</v>
+        <v>0.4189185994619038</v>
       </c>
     </row>
     <row r="7">
@@ -1091,35 +911,23 @@
           <t>se008731_01_40pcorr.ses</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
-        <v>7.689016800031823</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>0.2865434000341338</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>0.8840387999953236</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>1.468674599891528</v>
+      <c r="B7" s="21" t="n">
+        <v>8.674475400039228</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0.2718487994570751</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>0.6874216000142042</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>1.122007600497454</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.58136259998719</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>72.83512679987325</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>0.4674006000641384</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>0.3781879999223747</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>0.4102053999304189</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0.3752505999727873</v>
+        <v>10.69566540027154</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>0.3885980004270095</v>
       </c>
     </row>
     <row r="8">
@@ -1129,34 +937,22 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>8.507890799955931</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>0.1966133999303565</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>0.9642557999541168</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>0.8484605999910855</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <v>1.297316999989562</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>66.87853439998435</v>
-      </c>
-      <c r="H8" s="32" t="n">
-        <v>0.3811122000115574</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>0.3460349998931633</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.3172660000927863</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.3033135999430669</v>
+        <v>6.076872200355865</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.3042258002096787</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>0.8441048004897311</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>1.422286799788708</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>3.313653599616373</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.6052796001313254</v>
       </c>
     </row>
     <row r="10">
@@ -1199,27 +995,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>libhankel qwe</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht key 101</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht key 51</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht guptasarma</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>libhankel dht guptasarma fast</t>
+          <t>libhankel fftlog</t>
         </is>
       </c>
     </row>
@@ -1229,35 +1005,23 @@
           <t>sphere.ses</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="28" t="n">
         <v>0.009764475065043741</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="29" t="n">
         <v>0.0002032855524102355</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="30" t="n">
         <v>0.0001944508181386785</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="31" t="n">
         <v>0.0001024041351576086</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="32" t="n">
         <v>2.152009997787111e-05</v>
       </c>
-      <c r="G12" s="37" t="n">
-        <v>1.107131106050854e-05</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>0.0003681262252104515</v>
-      </c>
-      <c r="I12" s="39" t="n">
-        <v>0.001158578791637406</v>
-      </c>
-      <c r="J12" s="40" t="n">
-        <v>0.001359962438204312</v>
-      </c>
-      <c r="K12" s="41" t="n">
-        <v>0.002730464700358043</v>
+      <c r="G12" s="32" t="n">
+        <v>9.969797214210284e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1266,35 +1030,23 @@
           <t>spheres2micron.ses</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="28" t="n">
         <v>0.0004992532577444141</v>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C13" s="33" t="n">
         <v>0.0003480425306713427</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D13" s="34" t="n">
         <v>0.0003443025950119268</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="35" t="n">
         <v>0.0003243384622566044</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="32" t="n">
         <v>6.647456298723657e-06</v>
       </c>
-      <c r="G13" s="37" t="n">
-        <v>5.77369105689594e-06</v>
-      </c>
-      <c r="H13" s="33" t="n">
-        <v>0.02690750633253125</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>0.01328300251547565</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>0.001113297536936765</v>
-      </c>
-      <c r="K13" s="45" t="n">
-        <v>0.002761913154829045</v>
+      <c r="G13" s="32" t="n">
+        <v>8.130921430037412e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1303,35 +1055,23 @@
           <t>core_shell.ses</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="28" t="n">
         <v>0.0525109922389763</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="36" t="n">
         <v>0.004188762031374766</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="36" t="n">
         <v>0.004224379919300037</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="37" t="n">
         <v>0.002585516664657549</v>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F14" s="32" t="n">
         <v>5.697618781952893e-05</v>
       </c>
-      <c r="G14" s="37" t="n">
-        <v>4.402087932020407e-05</v>
-      </c>
-      <c r="H14" s="50" t="n">
-        <v>0.04487516359268222</v>
-      </c>
-      <c r="I14" s="51" t="n">
-        <v>0.01771728185647142</v>
-      </c>
-      <c r="J14" s="52" t="n">
-        <v>0.02672675577875266</v>
-      </c>
-      <c r="K14" s="33" t="n">
-        <v>0.05876782139580111</v>
+      <c r="G14" s="30" t="n">
+        <v>0.0009062296648186029</v>
       </c>
     </row>
     <row r="15">
@@ -1340,35 +1080,23 @@
           <t>se008724_01.ses</t>
         </is>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="38" t="n">
         <v>0.0001681662678487385</v>
       </c>
-      <c r="C15" s="53" t="n">
+      <c r="C15" s="28" t="n">
         <v>0.0003018481945323578</v>
       </c>
-      <c r="D15" s="53" t="n">
+      <c r="D15" s="39" t="n">
         <v>0.0002956897405317412</v>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="40" t="n">
         <v>0.0002487807663171994</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="41" t="n">
         <v>2.28770140301928e-05</v>
       </c>
-      <c r="G15" s="37" t="n">
-        <v>2.787570594185999e-05</v>
-      </c>
-      <c r="H15" s="55" t="n">
-        <v>0.003398085183560148</v>
-      </c>
-      <c r="I15" s="33" t="n">
-        <v>0.00365735298294778</v>
-      </c>
-      <c r="J15" s="56" t="n">
-        <v>0.001502271808433174</v>
-      </c>
-      <c r="K15" s="57" t="n">
-        <v>0.003090742876007344</v>
+      <c r="G15" s="32" t="n">
+        <v>6.061484524070663e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1377,35 +1105,23 @@
           <t>se008731_01_40pcorr.ses</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="28" t="n">
         <v>0.0004992532577441608</v>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="33" t="n">
         <v>0.0003480425306709867</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D16" s="34" t="n">
         <v>0.0003443025950129936</v>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E16" s="35" t="n">
         <v>0.000324338462257984</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="32" t="n">
         <v>6.647456298320468e-06</v>
       </c>
-      <c r="G16" s="37" t="n">
-        <v>5.773691056421339e-06</v>
-      </c>
-      <c r="H16" s="33" t="n">
-        <v>0.02690750633253728</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>0.01328300251547537</v>
-      </c>
-      <c r="J16" s="44" t="n">
-        <v>0.001113297536936963</v>
-      </c>
-      <c r="K16" s="45" t="n">
-        <v>0.002761913154828469</v>
+      <c r="G16" s="32" t="n">
+        <v>8.130921427887802e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1414,41 +1130,29 @@
           <t>SiO2_100pc_H2O_0pc_D2O.ses</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="28" t="n">
         <v>0.08978613167395876</v>
       </c>
-      <c r="C17" s="36" t="n">
+      <c r="C17" s="32" t="n">
         <v>5.323756268240784e-05</v>
       </c>
-      <c r="D17" s="58" t="n">
+      <c r="D17" s="42" t="n">
         <v>0.002444043102686319</v>
       </c>
-      <c r="E17" s="58" t="n">
+      <c r="E17" s="42" t="n">
         <v>0.002444042768850117</v>
       </c>
-      <c r="F17" s="58" t="n">
+      <c r="F17" s="42" t="n">
         <v>0.002444042894418752</v>
       </c>
-      <c r="G17" s="37" t="n">
-        <v>0.00244404334804751</v>
-      </c>
-      <c r="H17" s="58" t="n">
-        <v>0.002444042807574865</v>
-      </c>
-      <c r="I17" s="58" t="n">
-        <v>0.002444043011953478</v>
-      </c>
-      <c r="J17" s="58" t="n">
-        <v>0.002444042896645688</v>
-      </c>
-      <c r="K17" s="58" t="n">
-        <v>0.002444042893542574</v>
+      <c r="G17" s="42" t="n">
+        <v>0.002444044795461117</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
